--- a/AAII_Financials/Quarterly/GPCR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GPCR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="92">
   <si>
     <t>GPCR</t>
   </si>
@@ -656,108 +656,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -797,11 +805,11 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
@@ -824,8 +832,14 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -892,8 +906,14 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -960,8 +980,14 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -986,76 +1012,84 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>100100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>66500</v>
+      </c>
+      <c r="F12" s="3">
         <v>68700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>59000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>54700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>42900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>33500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>32600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>22100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>20700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>20000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>17500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>19400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>13100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>8400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>27800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>10200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>8500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>9900</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1122,52 +1156,58 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>2600</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>12400</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>3700</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1190,22 +1230,28 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>600</v>
+      </c>
+      <c r="E15" s="3">
+        <v>600</v>
+      </c>
+      <c r="F15" s="3">
         <v>700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>400</v>
-      </c>
-      <c r="F15" s="3">
-        <v>300</v>
-      </c>
-      <c r="G15" s="3">
-        <v>300</v>
       </c>
       <c r="H15" s="3">
         <v>300</v>
@@ -1214,16 +1260,16 @@
         <v>300</v>
       </c>
       <c r="J15" s="3">
+        <v>300</v>
+      </c>
+      <c r="K15" s="3">
+        <v>300</v>
+      </c>
+      <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>200</v>
-      </c>
-      <c r="L15" s="3">
-        <v>100</v>
-      </c>
-      <c r="M15" s="3">
-        <v>100</v>
       </c>
       <c r="N15" s="3">
         <v>100</v>
@@ -1232,10 +1278,10 @@
         <v>100</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1258,8 +1304,14 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1281,144 +1333,158 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>118600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>89400</v>
+      </c>
+      <c r="F17" s="3">
         <v>-13700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>73800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>70500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>56300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>47100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>45800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>33300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>32000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>31000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>26100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>26000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>19600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>13000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>39600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>14000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>13000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>13300</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-118600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-89400</v>
+      </c>
+      <c r="F18" s="3">
         <v>13700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-73800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-70500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-56300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-47100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-45800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-33300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-32000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-31000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-26100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-26000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-19600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-39600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-14000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-13000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-13300</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1443,13 +1509,15 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>13900</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>3</v>
@@ -1460,8 +1528,8 @@
       <c r="G20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H20" s="3">
-        <v>12900</v>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1484,26 +1552,26 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
+      <c r="V20" s="3">
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
@@ -1511,65 +1579,71 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>600</v>
+        <v>-118100</v>
       </c>
       <c r="E21" s="3">
+        <v>-88800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>14500</v>
+      </c>
+      <c r="G21" s="3">
         <v>-73400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-70200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-56000</v>
       </c>
-      <c r="H21" s="3">
-        <v>-59600</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
+        <v>-46800</v>
+      </c>
+      <c r="K21" s="3">
         <v>-45600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-33100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-31800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-30900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-26100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-25900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-19600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-39000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-13800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-13000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1579,8 +1653,14 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1620,11 +1700,11 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1647,76 +1727,88 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-105900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-75800</v>
+      </c>
+      <c r="F23" s="3">
         <v>33200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-65600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-61500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-46700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-36300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-33900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-26000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-26000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-24800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-23500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-23200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-18000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-39200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-13900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-13000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-13300</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1724,10 +1816,10 @@
         <v>200</v>
       </c>
       <c r="E24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G24" s="3">
         <v>100</v>
@@ -1742,40 +1834,40 @@
         <v>100</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24" s="3">
+        <v>100</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
-      </c>
-      <c r="R24" s="3">
-        <v>100</v>
-      </c>
-      <c r="S24" s="3">
-        <v>100</v>
       </c>
       <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
+      <c r="U24" s="3">
+        <v>100</v>
+      </c>
+      <c r="V24" s="3">
+        <v>100</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
@@ -1783,8 +1875,14 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1851,144 +1949,162 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-106200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="F26" s="3">
         <v>33000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-65700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-61700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-46800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-36500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-34000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-26000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-26000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-24500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-23900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-23300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-18000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-39400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-13900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-13100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-13400</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-106200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="F27" s="3">
         <v>33000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-65700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-61700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-46800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-36500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-34000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-26000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-26000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-24500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-23900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-23300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-18000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-41000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-15500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-13100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-15400</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2055,8 +2171,14 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2123,8 +2245,14 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2191,8 +2319,14 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2259,13 +2393,19 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-13900</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>3</v>
@@ -2276,8 +2416,8 @@
       <c r="G32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H32" s="3">
-        <v>-12900</v>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -2300,26 +2440,26 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>-900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
+      <c r="V32" s="3">
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
@@ -2327,76 +2467,88 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-106200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="F33" s="3">
         <v>33000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-65700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-61700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-46800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-36500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-34000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-26000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-26000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-24500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-23900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-23300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-18000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-41000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-15500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-13100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-15400</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2463,149 +2615,167 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-106200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="F35" s="3">
         <v>33000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-65700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-61700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-46800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-36500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-34000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-26000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-26000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-24500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-23900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-23300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-18000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-41000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-15500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-13100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-15400</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2630,8 +2800,10 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2656,59 +2828,61 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>272600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>316200</v>
+      </c>
+      <c r="F41" s="3">
         <v>799600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>102900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>147000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>152100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>169500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>172100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>381600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>97800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>129800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>50600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>40600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>126500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>26100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>28100</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2724,59 +2898,65 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1070000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1142300</v>
+      </c>
+      <c r="F42" s="3">
         <v>646600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>696100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>639500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>684800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>714000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>743200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>545500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>338600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>337500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>154800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>184000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>114400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>64800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>74700</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2792,20 +2972,26 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3">
         <v>100000</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2833,11 +3019,11 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -2860,8 +3046,14 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2901,11 +3093,11 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -2928,8 +3120,14 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2969,18 +3167,18 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>2200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2000</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2996,59 +3194,65 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1372000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1490600</v>
+      </c>
+      <c r="F46" s="3">
         <v>1570300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>814000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>799300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>849600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>891200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>923700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>937600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>449400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>473600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>210000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>228200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>246200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>93100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>104800</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3064,8 +3268,14 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3105,11 +3315,11 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3132,59 +3342,65 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F48" s="3">
         <v>12900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>11500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>10900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>10800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>7000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>7700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>7600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>7800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>8400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>6100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1400</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3200,8 +3416,14 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3268,8 +3490,14 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3336,8 +3564,14 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3404,40 +3638,46 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F52" s="3">
         <v>700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>6600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>6200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>6100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>5100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1800</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -3446,17 +3686,17 @@
         <v>100</v>
       </c>
       <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>100</v>
+      </c>
+      <c r="R52" s="3">
         <v>3500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2300</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,8 +3712,14 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3540,59 +3786,65 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1425400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1508100</v>
+      </c>
+      <c r="F54" s="3">
         <v>1583900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>832200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>816400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>866500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>903300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>933200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>947000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>457200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>482000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>216400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>229400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>247400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>97800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>108400</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,8 +3860,14 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3634,8 +3892,10 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3660,59 +3920,61 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F57" s="3">
         <v>13900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>17800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>9000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>8700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>8000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>8400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>6500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>4700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>5700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>4900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>6000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>5700</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3728,53 +3990,59 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F58" s="3">
         <v>2900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -3796,8 +4064,14 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3816,39 +4090,39 @@
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="J59" s="3">
-        <v>0</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
         <v>300</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>7000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>6500</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,59 +4138,65 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>66100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>57000</v>
+      </c>
+      <c r="F60" s="3">
         <v>63300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>57500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>39000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>36500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>36000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>33400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>22700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>23600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>24700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>20100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>15000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>11000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>13000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>12200</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,8 +4212,14 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3941,38 +4227,38 @@
         <v>3600</v>
       </c>
       <c r="E61" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F61" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G61" s="3">
         <v>4300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>5000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>5100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>3000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>3500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>4000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>3000</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4000,19 +4286,25 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>900</v>
+      </c>
+      <c r="F62" s="3">
         <v>600</v>
-      </c>
-      <c r="E62" s="3">
-        <v>300</v>
-      </c>
-      <c r="F62" s="3">
-        <v>300</v>
       </c>
       <c r="G62" s="3">
         <v>300</v>
@@ -4035,24 +4327,24 @@
       <c r="M62" s="3">
         <v>300</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3">
+      <c r="N62" s="3">
+        <v>300</v>
+      </c>
+      <c r="O62" s="3">
+        <v>300</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
         <v>100</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,8 +4360,14 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4136,8 +4434,14 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4204,8 +4508,14 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4272,59 +4582,65 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>61000</v>
+      </c>
+      <c r="F66" s="3">
         <v>67500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>62100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>44400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>41900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>38500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>36400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>26000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>27400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>29100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>23400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>15000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>11000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>13000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>12300</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4340,8 +4656,14 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4366,8 +4688,10 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4434,8 +4758,14 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4502,8 +4832,14 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4544,17 +4880,17 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>200000</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="S70" s="3">
         <v>200000</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4570,8 +4906,14 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4638,59 +4980,65 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-652400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-546300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-470300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-503300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-437600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-375900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-329100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-292600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-258600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-232600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-206600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-182100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-158200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-134900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-117000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-105100</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4706,8 +5054,14 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4774,8 +5128,14 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4842,8 +5202,14 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4910,59 +5276,65 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1354400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1447100</v>
+      </c>
+      <c r="F76" s="3">
         <v>1516400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>770000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>772100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>824600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>864800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>896800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>921000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>429800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>453000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>193000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>214400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>236400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-115100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-103900</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4978,8 +5350,14 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5046,149 +5424,167 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-106200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="F81" s="3">
         <v>33000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-65700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-61700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-46800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-36500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-34000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-26000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-26000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-24500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-23900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-23300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-18000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-41000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-15500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-13100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-15400</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5213,8 +5609,10 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5225,16 +5623,16 @@
         <v>300</v>
       </c>
       <c r="F83" s="3">
+        <v>300</v>
+      </c>
+      <c r="G83" s="3">
+        <v>300</v>
+      </c>
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>200</v>
-      </c>
-      <c r="H83" s="3">
-        <v>100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
@@ -5258,19 +5656,19 @@
         <v>100</v>
       </c>
       <c r="Q83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R83" s="3">
         <v>100</v>
       </c>
       <c r="S83" s="3">
+        <v>200</v>
+      </c>
+      <c r="T83" s="3">
         <v>100</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
+      <c r="U83" s="3">
+        <v>100</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
@@ -5281,8 +5679,14 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5349,8 +5753,14 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5417,8 +5827,14 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5485,8 +5901,14 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5553,8 +5975,14 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5621,65 +6049,71 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-120100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>15200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-64400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-51000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-54600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-52200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-36500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-19700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-26400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-34100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-21700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-20600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-16900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-20300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-34100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-10100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-13500</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5689,8 +6123,14 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5715,52 +6155,54 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-100</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R91" s="3">
         <v>-100</v>
@@ -5769,22 +6211,28 @@
         <v>-100</v>
       </c>
       <c r="T91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5851,8 +6299,14 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5919,65 +6373,71 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-496900</v>
+      </c>
+      <c r="F94" s="3">
         <v>56100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-49300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>48900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>34000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>33200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-189000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-204500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>1400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-180700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>30100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-68700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-49000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>10300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-72400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-16100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-39700</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5987,8 +6447,14 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6013,8 +6479,10 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6054,11 +6522,11 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -6081,8 +6549,14 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6149,8 +6623,14 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6217,8 +6697,14 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6285,65 +6771,71 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F100" s="3">
         <v>705000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>56200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>514700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>281600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>500</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-300</v>
-      </c>
-      <c r="O100" s="3">
-        <v>169700</v>
       </c>
       <c r="P100" s="3">
         <v>-300</v>
       </c>
       <c r="Q100" s="3">
+        <v>169700</v>
+      </c>
+      <c r="R100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S100" s="3">
         <v>29300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>31000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-1400</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6353,8 +6845,14 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6394,11 +6892,11 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -6421,65 +6919,71 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-43500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-483500</v>
+      </c>
+      <c r="F102" s="3">
         <v>696700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-44100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-5100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-17400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-209500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>283800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-32000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>79200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>10000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-85900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>100400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-77200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>4900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-54700</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6487,6 +6991,12 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
